--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2530-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2530-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{53DBFEA2-AF06-47E9-8642-FABD0C241E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{665063FA-B234-4AE5-AA07-F9D4771EF65E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{9DEDC85A-EFBF-471D-A6BE-A02FF6B4A248}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{EA4CB4E0-D1EE-4DC0-A3D0-D4C95C1A2837}"/>
   </bookViews>
   <sheets>
     <sheet name="2530-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1595,30 +1595,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD45662C-FBBC-43A3-9524-1477DB563232}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6D4721B-4529-4A8F-9261-AA09C56309BE}">
   <dimension ref="A1:X53"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -1652,7 +1652,7 @@
       <c r="W1" s="33"/>
       <c r="X1" s="25"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
@@ -1688,7 +1688,7 @@
       <c r="W2" s="35"/>
       <c r="X2" s="36"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="26" t="s">
         <v>2</v>
       </c>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="X3" s="39"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="28"/>
       <c r="B4" s="29"/>
       <c r="C4" s="7"/>
@@ -1808,7 +1808,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="40">
         <v>2025</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>6.84</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>28</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>28</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>4.07</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>28</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="42">
         <v>2024</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>28</v>
       </c>
@@ -2248,7 +2248,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>28</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>28</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>28</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="40">
         <v>2023</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>28</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>1.55</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>28</v>
       </c>
@@ -2690,7 +2690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>28</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="42">
         <v>2022</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>28</v>
       </c>
@@ -2910,7 +2910,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>28</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="40">
         <v>2021</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="42">
         <v>2020</v>
       </c>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="40">
         <v>2019</v>
       </c>
@@ -3200,7 +3200,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="42">
         <v>2018</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="40">
         <v>2017</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="42">
         <v>2016</v>
       </c>
@@ -3416,7 +3416,7 @@
         <v>6.06</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="40">
         <v>2015</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="42">
         <v>2014</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="40">
         <v>2013</v>
       </c>
@@ -3632,7 +3632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="42">
         <v>2012</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="40">
         <v>2011</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>6.44</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="44">
         <v>2010</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="46"/>
       <c r="B33" s="47"/>
       <c r="C33" s="20" t="s">
@@ -3876,7 +3876,7 @@
       <c r="W33" s="53"/>
       <c r="X33" s="49"/>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="54">
         <v>2009</v>
       </c>
@@ -3948,7 +3948,7 @@
         <v>7.84</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="56"/>
       <c r="B35" s="57"/>
       <c r="C35" s="22" t="s">
@@ -3976,7 +3976,7 @@
       <c r="W35" s="63"/>
       <c r="X35" s="59"/>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="42">
         <v>2008</v>
       </c>
@@ -4048,7 +4048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="40">
         <v>2007</v>
       </c>
@@ -4120,7 +4120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="42">
         <v>2006</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="40">
         <v>2005</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="42">
         <v>2004</v>
       </c>
@@ -4336,7 +4336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="40">
         <v>2003</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="42">
         <v>2002</v>
       </c>
@@ -4480,7 +4480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="40">
         <v>2001</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="42">
         <v>2000</v>
       </c>
@@ -4624,7 +4624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="40">
         <v>1999</v>
       </c>
@@ -4696,7 +4696,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="42">
         <v>1998</v>
       </c>
@@ -4768,7 +4768,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="40">
         <v>1997</v>
       </c>
@@ -4840,7 +4840,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="42">
         <v>1996</v>
       </c>
@@ -4912,7 +4912,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="40">
         <v>1995</v>
       </c>
@@ -4984,7 +4984,7 @@
         <v>7.73</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="42">
         <v>1994</v>
       </c>
@@ -5056,7 +5056,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="40">
         <v>1993</v>
       </c>
@@ -5128,7 +5128,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="42">
         <v>1992</v>
       </c>
@@ -5200,7 +5200,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="40" t="s">
         <v>61</v>
       </c>
